--- a/verification_forms/007_marketplace_partner_renewal_application_form--verification_forms.xlsx
+++ b/verification_forms/007_marketplace_partner_renewal_application_form--verification_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_page_1</t>
+          <t>partner_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>partner_name</t>
+          <t>Partner Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_page_2</t>
+          <t>partner_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>partner_type</t>
+          <t>Partner Type</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_page_3</t>
+          <t>renewal_date</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>renewal_date</t>
+          <t>Renewal Date</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_page_4</t>
+          <t>contact_number</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>Contact Number</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_page_5</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_page_6</t>
+          <t>partner_address</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>partner_address</t>
+          <t>Partner Address</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,58 +658,58 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_page_7</t>
+          <t>partner_website</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>partner_website</t>
+          <t>Partner Website</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_page_8</t>
+          <t>renewal_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>partner_notes</t>
+          <t>Renewal Status</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_page_9</t>
+          <t>status_update</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>renewal_status</t>
+          <t>Status Update</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,40 +722,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_page_10</t>
+          <t>submission_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>status_update</t>
+          <t>Submission Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_page_11</t>
+          <t>reviewer_comments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>Reviewer Comments</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,40 +768,40 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_page_12</t>
+          <t>reviewer_signature</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>partner_review</t>
+          <t>Reviewer Signature</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_page_13</t>
+          <t>reviewer_notes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>Reviewer Notes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>form_page_14</t>
+          <t>partner_signature</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>reviewer</t>
+          <t>Partner Signature</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,246 +842,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form_page_15</t>
+          <t>partner_notes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>reviewer_comments</t>
+          <t>Partner Notes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>form_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>status_update</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>form_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>reviewer_comments</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>reviewer_signature</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>reviewer_notes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>partner_signature</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>partner_notes</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>status_update</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,102 +896,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_page_2_choices</t>
+          <t>partner_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>partner_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Partner A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_page_2_choices</t>
+          <t>partner_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>partner_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Partner B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_page_9_choices</t>
+          <t>renewal_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_page_9_choices</t>
+          <t>renewal_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_page_12_choices</t>
+          <t>renewal_status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>form_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>option2</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>option2</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
